--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119895658</v>
+        <v>119895656</v>
       </c>
       <c r="B3" t="n">
-        <v>57201</v>
+        <v>56655</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,14 +832,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -895,6 +895,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>46+10+6</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119895656</v>
+        <v>119895658</v>
       </c>
       <c r="B4" t="n">
-        <v>56655</v>
+        <v>57201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,20 +938,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100065</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,14 +961,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1019,11 +1024,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>46+10+6</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119895656</v>
+        <v>119895658</v>
       </c>
       <c r="B3" t="n">
-        <v>56655</v>
+        <v>57201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,14 +832,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -895,11 +895,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>46+10+6</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +921,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119895658</v>
+        <v>119895656</v>
       </c>
       <c r="B4" t="n">
-        <v>57201</v>
+        <v>56655</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,20 +933,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -961,14 +956,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1024,6 +1019,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>46+10+6</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119895658</v>
+        <v>119895656</v>
       </c>
       <c r="B3" t="n">
-        <v>57201</v>
+        <v>56665</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,14 +832,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -897,6 +897,11 @@
           <t>16:00</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>46+10+6</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -914,17 +919,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119895656</v>
+        <v>119895658</v>
       </c>
       <c r="B4" t="n">
-        <v>56655</v>
+        <v>57211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,20 +938,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100065</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,14 +961,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1021,11 +1026,6 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>46+10+6</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119895656</v>
+        <v>119895658</v>
       </c>
       <c r="B3" t="n">
-        <v>56665</v>
+        <v>57211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Accipiter gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,14 +832,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -897,11 +897,6 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>46+10+6</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -919,17 +914,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119895658</v>
+        <v>119895656</v>
       </c>
       <c r="B4" t="n">
-        <v>57211</v>
+        <v>56665</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,20 +933,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -961,14 +956,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1026,6 +1021,11 @@
           <t>16:00</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>46+10+6</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,124 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123442877</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56590</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bredemad 300 meter öster om, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>435047</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6302586</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,6 +1166,120 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123705301</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58023</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bredemad 300 meter öster om, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>435047</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6302586</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Roger Karlsson, Kerstin Karlsson, Stig Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>123442877</v>
       </c>
       <c r="B5" t="n">
-        <v>56590</v>
+        <v>56596</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>123705301</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58029</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>123442877</v>
       </c>
       <c r="B5" t="n">
-        <v>56596</v>
+        <v>56599</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>123705301</v>
       </c>
       <c r="B6" t="n">
-        <v>58029</v>
+        <v>58032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1171,7 +1171,7 @@
         <v>123705301</v>
       </c>
       <c r="B6" t="n">
-        <v>58032</v>
+        <v>58033</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124235830</v>
+        <v>124235846</v>
       </c>
       <c r="B7" t="n">
-        <v>58016</v>
+        <v>57143</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102995</v>
+        <v>102963</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1317,18 +1317,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1376,6 +1372,11 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>cirka antal</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1393,17 +1394,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124235846</v>
+        <v>124235830</v>
       </c>
       <c r="B8" t="n">
-        <v>57143</v>
+        <v>58016</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,16 +1417,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102963</v>
+        <v>102995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,14 +1436,18 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1490,11 +1495,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>cirka antal</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1512,10 +1512,134 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124744803</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57421</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bredemad 300 meter öster om, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>435047</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6302586</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124235846</v>
+        <v>124235830</v>
       </c>
       <c r="B7" t="n">
-        <v>57143</v>
+        <v>58016</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102963</v>
+        <v>102995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1317,14 +1317,18 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1370,11 +1374,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>cirka antal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,10 +1400,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124235830</v>
+        <v>124235846</v>
       </c>
       <c r="B8" t="n">
-        <v>58016</v>
+        <v>57143</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,16 +1416,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102995</v>
+        <v>102963</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1436,18 +1435,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1493,6 +1488,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>cirka antal</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124235830</v>
+        <v>124235846</v>
       </c>
       <c r="B7" t="n">
-        <v>58016</v>
+        <v>57143</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102995</v>
+        <v>102963</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1317,18 +1317,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1376,6 +1372,11 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>cirka antal</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1393,17 +1394,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124235846</v>
+        <v>124235830</v>
       </c>
       <c r="B8" t="n">
-        <v>57143</v>
+        <v>58016</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,16 +1417,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102963</v>
+        <v>102995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1435,14 +1436,18 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1490,11 +1495,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>cirka antal</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1282,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124235846</v>
+        <v>124235830</v>
       </c>
       <c r="B7" t="n">
-        <v>57143</v>
+        <v>58016</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102963</v>
+        <v>102995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1317,14 +1317,18 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1372,11 +1376,6 @@
           <t>2025-04-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>cirka antal</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1394,17 +1393,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124235830</v>
+        <v>124235846</v>
       </c>
       <c r="B8" t="n">
-        <v>58016</v>
+        <v>57143</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,16 +1416,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102995</v>
+        <v>102963</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1436,18 +1435,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1495,6 +1490,11 @@
           <t>2025-04-19</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>cirka antal</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1522,7 +1522,7 @@
         <v>124744803</v>
       </c>
       <c r="B9" t="n">
-        <v>57421</v>
+        <v>57573</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1641,6 +1641,115 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126055672</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57017</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tofsvipa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Vanellus vanellus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bredemad 300 meter öster om, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>435047</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6302586</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1646,7 +1646,7 @@
         <v>126055672</v>
       </c>
       <c r="B10" t="n">
-        <v>57017</v>
+        <v>57018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1646,7 +1646,7 @@
         <v>126055672</v>
       </c>
       <c r="B10" t="n">
-        <v>57018</v>
+        <v>57022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1745,7 +1745,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1646,7 +1646,7 @@
         <v>126055672</v>
       </c>
       <c r="B10" t="n">
-        <v>57022</v>
+        <v>57023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1285,12 +1285,7 @@
         <v>124235830</v>
       </c>
       <c r="B7" t="n">
-        <v>58016</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1285,7 +1285,7 @@
         <v>124235830</v>
       </c>
       <c r="B7" t="n">
-        <v>58235</v>
+        <v>58240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1285,7 +1285,7 @@
         <v>124235830</v>
       </c>
       <c r="B7" t="n">
-        <v>58240</v>
+        <v>58241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1285,7 +1285,7 @@
         <v>124235830</v>
       </c>
       <c r="B7" t="n">
-        <v>58241</v>
+        <v>58243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1285,7 +1285,7 @@
         <v>124235830</v>
       </c>
       <c r="B7" t="n">
-        <v>58243</v>
+        <v>58246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -1285,7 +1285,7 @@
         <v>124235830</v>
       </c>
       <c r="B7" t="n">
-        <v>58246</v>
+        <v>58247</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105237256</v>
+        <v>119895658</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bredemads avfallsanläggning, Sm</t>
+          <t>Bredemad 300 meter öster om, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434981.038307771</v>
+        <v>435047</v>
       </c>
       <c r="R2" t="n">
-        <v>6302477.231333919</v>
+        <v>6302586</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-05</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnag på gran. JMN0090 (Calluna AB) Naturvärdesinventering</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,44 +782,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Roger Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119895658</v>
+        <v>105237260</v>
       </c>
       <c r="B3" t="n">
-        <v>57211</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,29 +822,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredemad 300 meter öster om, Sm</t>
+          <t>Bredemads avfallsanläggning, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435047</v>
+        <v>434858</v>
       </c>
       <c r="R3" t="n">
-        <v>6302586</v>
+        <v>6302464</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,22 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hackmärken. JMN0090 (Calluna AB) Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,12 +889,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Roger Karlsson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -924,12 +904,7 @@
         <v>119895656</v>
       </c>
       <c r="B4" t="n">
-        <v>56665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,53 +1025,44 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123442877</v>
+        <v>124744803</v>
       </c>
       <c r="B5" t="n">
-        <v>56621</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102932</v>
+        <v>100082</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1136,12 +1102,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,15 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123705301</v>
+        <v>105237256</v>
       </c>
       <c r="B6" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,46 +1155,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredemad 300 meter öster om, Sm</t>
+          <t>Bredemads avfallsanläggning, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>435047</v>
+        <v>434981</v>
       </c>
       <c r="R6" t="n">
-        <v>6302586</v>
+        <v>6302477</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1250,12 +1214,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnag på gran. JMN0090 (Calluna AB) Naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,22 +1239,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Karlsson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson, Stig Svensson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124235830</v>
+        <v>123442877</v>
       </c>
       <c r="B7" t="n">
-        <v>58247</v>
+        <v>57105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,32 +1262,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102995</v>
+        <v>102932</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1363,12 +1332,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,32 +1364,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124235846</v>
+        <v>126055672</v>
       </c>
       <c r="B8" t="n">
-        <v>57143</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102963</v>
+        <v>102952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1430,14 +1394,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1477,17 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>cirka antal</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,32 +1473,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124744803</v>
+        <v>124235846</v>
       </c>
       <c r="B9" t="n">
-        <v>57573</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57546</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100082</v>
+        <v>102963</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1549,14 +1503,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1596,22 +1550,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>cirka antal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,27 +1587,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126055672</v>
+        <v>123705301</v>
       </c>
       <c r="B10" t="n">
-        <v>57023</v>
+        <v>58497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102952</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1668,14 +1617,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1715,12 +1664,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,10 +1689,230 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>Roger Karlsson, Kerstin Karlsson, Stig Svensson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124235830</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58463</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bredemad 300 meter öster om, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>435047</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6302586</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
           <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105237257</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bredemads avfallsanläggning, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>434969</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6302477</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnag på gran. JMN0090 (Calluna AB) Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29270-2023 artfynd.xlsx
+++ b/artfynd/A 29270-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119895658</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105237260</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119895656</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124744803</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1248,6 +1273,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105237256</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123442877</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126055672</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124235846</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1693,6 +1738,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123705301</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124235830</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1913,8 +1968,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105237257</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>